--- a/output/spreadsheet/t01-04-器具类别与规格词典-260928.xlsx
+++ b/output/spreadsheet/t01-04-器具类别与规格词典-260928.xlsx
@@ -15740,7 +15740,7 @@
       </c>
       <c r="J39" s="8" t="str">
         <f>INDEX('01_公共字段'!$F$6:$F$65,MATCH($A39,'01_公共字段'!$A$6:$A$65,0))</f>
-        <v>不是每件独立护甲HP，不与灵障合并；基础模板与本件结果分别引用，不按另一同名成品的材料选择串值。</v>
+        <v>不是每件独立护甲HP，不与灵盾合并；基础模板与本件结果分别引用，不按另一同名成品的材料选择串值。</v>
       </c>
       <c r="K39" s="8" t="str">
         <f>INDEX('01_公共字段'!$H$6:$H$65,MATCH($A39,'01_公共字段'!$A$6:$A$65,0))</f>
@@ -19843,8 +19843,10 @@
       <c r="C44" s="1" t="s">
         <v>1536</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>1537</v>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>我建议支持以下成本类型：；基础资源；气血；灵力；体力；防御资源；护甲；普通灵盾；指定特殊盾；状态资源；指定Buff层数；指定Debuff层数；例如：；消耗3附炎。；器具内部资源；充能；阶段值；次数；实体资源；丹药数量；符箓数量；暗器数量；特殊材料/弹药；使用寿命；耐久；本场使用次数；耐久体系我们还没有正式决定要不要大范围采用，所以这里只留接口，不代表必须做装备修理。</t>
+        </is>
       </c>
       <c r="E44" s="1" t="s">
         <v>1512</v>
@@ -21103,8 +21105,10 @@
       <c r="C86" s="1" t="s">
         <v>1666</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>1667</v>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>《青冥破空诀》第八重【贯日】使【青冥贯日】风属性＋穿刺标签的**本体直接伤害＋40%**；本次伤害经护盾后实际进入护甲层的部分，再获得**＋15个百分点入甲伤害修正**。该入甲加成不回溯增加特殊盾或灵盾的吸收量，增幅后先扣护甲、打穿后的余伤可扣气血，见5.41。本术仍只是一件法术的一次主动攻击事件，双标签不重复计算基础伤害。【贯日】与同重【逐隙】二选一。</t>
+        </is>
       </c>
       <c r="E86" s="1" t="s">
         <v>1579</v>
@@ -21463,8 +21467,10 @@
       <c r="C98" s="1" t="s">
         <v>1702</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>1703</v>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>本体没有斩击、穿刺、钝击标签的**纯属性法术**面对无甲、轻甲、重甲时，甲型伤害倍率**均为100%**，不因甲型另增伤或减伤。这不绕过特殊盾、灵盾或实际护甲值，也不取消5.1～5.2已定的属性身甲相克增减成。带斩击／穿刺／钝击标签的法术仍以法术为来源，但对应物理甲型标签按既有矩阵另算；同一基础伤害只计一次，与属性修正按既定规则相加。</t>
+        </is>
       </c>
       <c r="E98" s="1" t="s">
         <v>1579</v>
@@ -22390,8 +22396,10 @@
       <c r="B129" s="1" t="s">
         <v>1576</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>1786</v>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>docs\combat-system-design-2026-09-18.md｜## 4. 灵盾、逐层雷盾与剑幕｜原扫描L90</t>
+        </is>
       </c>
       <c r="D129" s="1" t="s">
         <v>1787</v>
@@ -22453,8 +22461,10 @@
       <c r="C131" s="1" t="s">
         <v>1792</v>
       </c>
-      <c r="D131" s="1" t="s">
-        <v>1793</v>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>| 伤害防御 | 先消耗护甲，溢出扣气血；三防具轮转补甲／上限叠加，衣甲记录甲型；无固定减伤 | 拆包／双标签、完整来源判定、甲型倍率、灵盾／雷盾 |</t>
+        </is>
       </c>
       <c r="E131" s="1" t="s">
         <v>1579</v>
@@ -64048,8 +64058,10 @@
       <c r="B68" s="1" t="s">
         <v>3691</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>3810</v>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>护甲值不等于灵盾/护盾</t>
+        </is>
       </c>
       <c r="D68" s="1" t="s">
         <v>3693</v>
@@ -67585,7 +67597,7 @@
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>不是每件独立护甲HP，不与灵障合并；基础模板与本件结果分别引用，不按另一同名成品的材料选择串值。</t>
+          <t>不是每件独立护甲HP，不与灵盾合并；基础模板与本件结果分别引用，不按另一同名成品的材料选择串值。</t>
         </is>
       </c>
       <c r="G39" s="1" t="s">
@@ -70476,8 +70488,10 @@
       <c r="D22" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>813</v>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>没有每件防具独立Armor HP；不与灵盾／特殊盾合成一个防御值。</t>
+        </is>
       </c>
       <c r="F22" s="1" t="s">
         <v>752</v>
